--- a/evaluation_forms/025_family_counseling_progress_note--evaluation_forms.xlsx
+++ b/evaluation_forms/025_family_counseling_progress_note--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Has the client shown improvement</t>
+          <t>Family Counseling Progress Question4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Has the client shown improvement</t>
+          <t>Family Counseling Progress Question5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Family progress notes</t>
+          <t>Family Counseling Progress Question6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Response to therapy</t>
+          <t>Family Counseling Progress Question9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Has the client responded</t>
+          <t>Family Counseling Progress Question14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Has the client responded</t>
+          <t>Family Counseling Progress Question15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Response to treatment</t>
+          <t>Family Counseling Progress Question18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Has the family responded</t>
+          <t>Family Counseling Progress Question21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Family response</t>
+          <t>Family Counseling Progress Question23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Response to intervention</t>
+          <t>Family Counseling Progress Question24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Response to interventions</t>
+          <t>Family Counseling Progress Question25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
